--- a/documents/4_growth/01_strategy/revenue-model.xlsx
+++ b/documents/4_growth/01_strategy/revenue-model.xlsx
@@ -2129,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" style="93" min="1" max="1"/>
@@ -2314,6 +2314,22 @@
           <t>【協議中・6/12】来週「50店舗以上」のPR TIMES配信予定。表記は「全国100店舗以上」で決め打ちする案を含め1〜2週間で決定。バイク数（約360台、CycleTrip300台超え）も訴求に使う方向</t>
         </is>
       </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" s="93">
+      <c r="A12" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>PAY.JPの契約プランと実際の決済手数料率（公表は3.3%。契約書か管理画面で確認）</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>店舗の合計負担率（現在は15%+3.3%=18.3%で記載）が確定する。Stripe載せ替え時のコスト比較の前提にもなる</t>
+        </is>
+      </c>
+      <c r="D12" s="83" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2326,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="93" min="1" max="1"/>
@@ -2388,7 +2404,7 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>98_presentations/pay.jp/asis.html（手数料15%・カード手数料3.5%店舗負担・ライド開始時課金・店頭決済の未請求フォールバック）</t>
+          <t>98_presentations/pay.jp/asis.html（手数料15%・カード手数料3.3%店舗負担・ライド開始時課金・店頭決済の未請求フォールバック）</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2617,7 @@
     <row r="29" ht="15" customHeight="1" s="93">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>カード手数料3.5%は店舗負担</t>
+          <t>カード手数料3.3%は店舗負担</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
@@ -2611,7 +2627,7 @@
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>98_presentations/pay.jp/asis.html（決済フロー仕様）</t>
+          <t>PAY.JP公表のスタンダード料率 https://pay.jp/plan （2026年6月時点・2026-09-14再確認）。旧値「約3.5%」からの訂正は本シート下部の訂正履歴を参照</t>
         </is>
       </c>
     </row>
@@ -3020,6 +3036,30 @@
       <c r="B59" s="103" t="inlineStr">
         <is>
           <t>紙請求の累計額×DB記録の突合は不要と判断（瀬野さん）。理由: 請求は紙で適切に実施できており（15%で請求していたと思われる・未検証）、検証より見える化（カード1本化）を優先。タスクリストからも#29を削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="84" t="inlineStr">
+        <is>
+          <t>■ 訂正履歴（2026-09-14）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="85" t="inlineStr">
+        <is>
+          <t>2026-09-14 カード手数料</t>
+        </is>
+      </c>
+      <c r="B62" s="106" t="inlineStr">
+        <is>
+          <t>旧「約3.5%（As-Isフロー資料の概算）」→ 新「3.3%（PAY.JP公表スタンダード料率・2026年6月時点）」。旧値は消さず履歴として残す。連動して 店舗負担計 18.5%→18.3% / 1万円決済の例 約350円→330円 / 店舗の手取り 8,150円→8,170円 を修正</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>理由: 「約3.5%」は payjp-flow-asis.md が1万円決済を「約350円」と書いた概算が起点で、HTML経由で本ブックへ出典として伝わった数字。PAY.JP公表料金はスタンダード3.3%・ビジネス2.78%・エンタープライズ2.59%/2.7%で、Platform（テナント型）も同じ料率表。3.5%は現行の公表料金に無い（3.5%はPayPay物販の料率）。3.3%は2026年6月に payjp-vs-stripe-comparison.md §2 が公式料金を再調査して採った値。根拠: https://pay.jp/plan （2026-09-14確認）。契約上の実料率は要確認（確認リスト#8）</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3140,7 @@
     <row r="7" ht="15" customHeight="1" s="93">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>カード手数料 約3.5%</t>
+          <t>カード手数料 3.3%</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -3110,7 +3150,7 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>決済フローAs-Is</t>
+          <t>決済フローAs-Is。PAY.JP公表のスタンダード料率（2026年6月時点）。契約上の実料率はPAY.JP管理画面で要確認</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3162,7 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
@@ -3507,7 +3547,7 @@
     <row r="11">
       <c r="A11" s="87" t="inlineStr">
         <is>
-          <t>・構造問題: カード手数料3.5%は店舗負担のため、店舗には店頭決済に誘導する動機がある（88%が店頭決済）</t>
+          <t>・構造問題: カード手数料3.3%は店舗負担のため、店舗には店頭決済に誘導する動機がある（88%が店頭決済）</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3852,7 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>月額0円・従量のみ。カード手数料3.5%は店舗負担</t>
+          <t>月額0円・従量のみ。カード手数料3.3%は店舗負担（PAY.JP公表のスタンダード料率（2026年6月時点）。契約上の実料率はPAY.JP管理画面で要確認）</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4892,7 @@
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>店舗負担計18.5%＝上限。これ以上触らない</t>
+          <t>店舗負担計18.3%＝上限。これ以上触らない</t>
         </is>
       </c>
     </row>
